--- a/artfynd/A 55776-2021 artfynd.xlsx
+++ b/artfynd/A 55776-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55776-2021 artfynd.xlsx
+++ b/artfynd/A 55776-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89472137</v>
+        <v>89472169</v>
       </c>
       <c r="B2" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>306054.9832432284</v>
+        <v>306055</v>
       </c>
       <c r="R2" t="n">
-        <v>6463017.126797871</v>
+        <v>6463017</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,19 +747,9 @@
           <t>2020-12-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-12-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89472215</v>
+        <v>89472184</v>
       </c>
       <c r="B3" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>2389</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>306054.9832432284</v>
+        <v>306055</v>
       </c>
       <c r="R3" t="n">
-        <v>6463017.126797871</v>
+        <v>6463017</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,19 +849,9 @@
           <t>2020-12-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-12-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89472184</v>
+        <v>89472137</v>
       </c>
       <c r="B4" t="n">
-        <v>95187</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2389</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>306054.9832432284</v>
+        <v>306055</v>
       </c>
       <c r="R4" t="n">
-        <v>6463017.126797871</v>
+        <v>6463017</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,19 +951,9 @@
           <t>2020-12-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-12-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89472169</v>
+        <v>89472215</v>
       </c>
       <c r="B5" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>306054.9832432284</v>
+        <v>306055</v>
       </c>
       <c r="R5" t="n">
-        <v>6463017.126797871</v>
+        <v>6463017</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1103,19 +1053,9 @@
           <t>2020-12-06</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-12-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,12 +1086,7 @@
         <v>95503549</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>306054.9832432284</v>
+        <v>306055</v>
       </c>
       <c r="R6" t="n">
-        <v>6463017.126797871</v>
+        <v>6463017</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,19 +1168,9 @@
           <t>2021-08-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-08-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 55776-2021 artfynd.xlsx
+++ b/artfynd/A 55776-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89472169</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89472184</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89472137</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89472215</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,8 +1229,20 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95503549</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>